--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1443,18 +1447,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,14 +1575,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1611,18 +1615,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1632,51 +1636,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,14 +1684,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1720,13 +1724,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1759,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1790,13 +1794,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1829,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1841,59 +1845,51 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Flood risk area</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1901,17 +1897,17 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1916,7 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1928,12 +1924,12 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1947,7 +1943,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1955,17 +1951,17 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1970,7 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1982,7 +1978,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2001,7 +1997,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2009,12 +2005,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2024,11 +2020,19 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2036,12 +2040,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2051,19 +2055,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2071,17 +2067,17 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2086,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2098,7 +2094,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2113,11 +2109,19 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2125,34 +2129,26 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2160,7 +2156,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2179,7 +2175,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2187,7 +2183,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2206,7 +2202,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2214,7 +2210,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2229,11 +2225,19 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2241,12 +2245,12 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2258,17 +2262,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2276,7 +2280,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2291,19 +2295,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2311,12 +2307,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2330,7 +2326,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2338,12 +2334,12 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2353,11 +2349,19 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Designated areas</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Designations[]</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2365,12 +2369,12 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2382,30 +2386,34 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Designated areas</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2415,16 +2423,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2432,14 +2432,14 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2489,19 +2489,19 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2525,14 +2525,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2578,28 +2578,32 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Equipment and method</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Total FTE</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2611,30 +2615,34 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Equipment and method</t>
+          <t>Existing use</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2644,16 +2652,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2661,24 +2661,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2718,24 +2718,20 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2749,7 +2745,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2757,17 +2753,17 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2772,7 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2784,12 +2780,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2803,7 +2799,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2811,17 +2807,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2826,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2838,7 +2834,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2857,7 +2853,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2865,7 +2861,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2884,7 +2880,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2892,26 +2888,34 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2919,34 +2923,26 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2954,17 +2950,17 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2969,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Produce foul sewage</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -2981,17 +2977,17 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2996,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Connect to drainage system (oil and gas)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3008,12 +3004,12 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3027,20 +3023,24 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3050,28 +3050,32 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent required</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3081,19 +3085,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
+          <t>Hazardous substance consent details</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3101,58 +3097,62 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3191,24 +3191,28 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3227,23 +3231,23 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3262,23 +3266,27 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3310,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3331,32 +3339,24 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3365,24 +3365,20 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3392,11 +3388,19 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3404,34 +3408,26 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3439,7 +3435,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3458,25 +3454,33 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3495,13 +3499,13 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3511,7 +3515,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3530,13 +3534,13 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3565,13 +3569,13 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3600,13 +3604,13 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -3616,7 +3620,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3630,23 +3634,19 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3660,24 +3660,20 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3691,15 +3687,19 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3723,19 +3723,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3749,29 +3749,25 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3776,7 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -3788,12 +3784,12 @@
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3807,7 +3803,7 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -3815,7 +3811,7 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3834,7 +3830,7 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -3842,7 +3838,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -3857,11 +3853,19 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -3869,34 +3873,26 @@
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -3904,7 +3900,7 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3923,7 +3919,7 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
@@ -3931,7 +3927,7 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3950,7 +3946,7 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>New public road</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -3958,7 +3954,7 @@
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -3977,7 +3973,7 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>Temporary right of way changes</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -3985,7 +3981,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4004,7 +4000,7 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
@@ -4012,7 +4008,7 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -4031,20 +4027,24 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4054,8 +4054,16 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="2" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Additional materials and specifications that form part of the planning application</t>
+        </is>
+      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Supporting documents[]</t>
@@ -4085,31 +4093,19 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
-        </is>
-      </c>
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Inspection address</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4124,11 +4120,19 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -4136,12 +4140,12 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4151,19 +4155,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -4171,17 +4167,17 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4186,7 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
@@ -4198,7 +4194,7 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -4217,7 +4213,7 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
@@ -4225,7 +4221,7 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -4244,7 +4240,7 @@
       <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
@@ -4252,7 +4248,7 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -4267,24 +4263,36 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="n"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -4294,16 +4302,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -4311,19 +4311,19 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -4342,14 +4342,14 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4373,19 +4373,19 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -4497,19 +4497,19 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4550,23 +4550,31 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="2" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Site ownership</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+        </is>
+      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Site owner</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -4576,21 +4584,13 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
-        </is>
-      </c>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Site owner</t>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4624,19 +4624,15 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Applicant interest</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Description of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4655,7 +4651,7 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
+          <t>Applicant interest adjoining land</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
@@ -4663,7 +4659,7 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4678,11 +4674,19 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n"/>
-      <c r="B133" s="2" t="n"/>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
@@ -4690,12 +4694,12 @@
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4705,19 +4709,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
@@ -4725,12 +4721,12 @@
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4744,7 +4740,7 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
@@ -4752,17 +4748,17 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4771,15 +4767,19 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4834,14 +4834,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4856,23 +4856,27 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="2" t="n"/>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Storage facilities</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+        </is>
+      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Storage facilities description</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4889,17 +4893,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities</t>
+          <t>Trade effluent</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4907,12 +4911,12 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4922,19 +4926,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4942,26 +4938,34 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -4969,34 +4973,26 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5004,7 +5000,7 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -5019,11 +5015,20 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n"/>
-      <c r="B144" s="2" t="n"/>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
+        </is>
+      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Oil and gas permission types[]</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5031,12 +5036,12 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -5046,33 +5051,28 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission types</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
-        </is>
-      </c>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -5091,19 +5091,19 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Oil and gas permission type</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5122,19 +5122,19 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission type</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -5153,14 +5153,14 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Condition number</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5179,19 +5179,15 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Condition number</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5210,7 +5206,7 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
+          <t>Will consolidate permissions</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
@@ -5218,17 +5214,17 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5233,7 @@
       <c r="B151" s="2" t="n"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr"/>
@@ -5245,17 +5241,17 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5264,15 +5260,19 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5296,19 +5296,19 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Application type</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -5327,19 +5327,19 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Application type</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5349,28 +5349,32 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="2" t="n"/>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Development phase</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -5380,19 +5384,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
-        </is>
-      </c>
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr"/>
@@ -5400,12 +5396,12 @@
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -5419,7 +5415,7 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr"/>
@@ -5427,12 +5423,12 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -5446,7 +5442,7 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr"/>
@@ -5454,7 +5450,7 @@
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5464,7 +5460,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5469,7 @@
       <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
@@ -5481,17 +5477,17 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5496,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5508,17 +5504,17 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5523,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5535,12 +5531,12 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Who provided the site hectares value (applicant or system)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5554,7 +5550,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Environmental statement</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5562,17 +5558,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Is an Environmental Statement attached to the application</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5577,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Environmental statement reference</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5589,26 +5585,34 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Reference to the environmental statement document</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Draft agreement included</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5616,34 +5620,26 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Agreement summary</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5651,42 +5647,15 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Summary of the agreement</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Agreement summary</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="inlineStr"/>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Summary of the agreement</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5694,66 +5663,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="A92:A106"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="B145:B155"/>
-    <mergeCell ref="A140"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="B134:B139"/>
-    <mergeCell ref="B107:B113"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A116:A120"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A145:A155"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="B59"/>
-    <mergeCell ref="B66"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="B140"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A141:A142"/>
-    <mergeCell ref="B67:B76"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A156:A164"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="A121:A129"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A107:A113"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="A66"/>
-    <mergeCell ref="A134:A139"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="B92:B106"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B156:B164"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B121:B129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B116:B120"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B91:B105"/>
+    <mergeCell ref="A83:A90"/>
+    <mergeCell ref="B139"/>
+    <mergeCell ref="A59:A64"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A76:A80"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A115:A119"/>
+    <mergeCell ref="A120:A128"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="A144:A154"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B54"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A106:A112"/>
+    <mergeCell ref="A133:A138"/>
+    <mergeCell ref="A155:A163"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="B58"/>
+    <mergeCell ref="A91:A105"/>
+    <mergeCell ref="A129:A132"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A54"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="B155:B163"/>
+    <mergeCell ref="B83:B90"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A139"/>
+    <mergeCell ref="B144:B154"/>
+    <mergeCell ref="B129:B132"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B133:B138"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B120:B128"/>
+    <mergeCell ref="B41:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -3196,13 +3196,13 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">

--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -5134,7 +5134,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">

--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">

--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1443,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,18 +1575,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1596,7 +1592,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1615,18 +1611,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1636,47 +1632,51 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,18 +1684,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1705,7 +1701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1720,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1759,13 +1755,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,13 +1790,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1829,13 +1825,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1845,51 +1841,59 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1897,17 +1901,17 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1920,7 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1924,12 +1928,12 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1943,7 +1947,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1951,17 +1955,17 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1978,7 +1982,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1997,7 +2001,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2005,12 +2009,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2020,19 +2024,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2040,12 +2036,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2055,11 +2051,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2067,17 +2071,17 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2090,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2094,7 +2098,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2109,19 +2113,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2129,26 +2125,34 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2156,7 +2160,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2175,7 +2179,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2183,7 +2187,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2202,7 +2206,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2210,7 +2214,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2225,19 +2229,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2245,12 +2241,12 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2262,17 +2258,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2280,7 +2276,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2295,11 +2291,19 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2307,12 +2311,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2326,7 +2330,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2334,12 +2338,12 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2349,19 +2353,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Designated areas</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2369,12 +2365,12 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2386,34 +2382,30 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>Designated areas</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Designations[]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2423,8 +2415,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2432,19 +2432,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2463,19 +2463,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2489,24 +2489,24 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2525,19 +2525,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2556,19 +2556,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2578,32 +2578,28 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Equipment and method</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Total FTE</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2615,34 +2611,30 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Existing use</t>
+          <t>Equipment and method</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2652,8 +2644,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2661,24 +2661,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2718,20 +2718,24 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2745,7 +2749,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2753,17 +2757,17 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2776,7 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2780,12 +2784,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2799,7 +2803,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2807,17 +2811,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2830,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2834,7 +2838,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2853,7 +2857,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2861,7 +2865,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2880,7 +2884,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2888,34 +2892,26 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2923,26 +2919,34 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2950,17 +2954,17 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2973,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -2977,17 +2981,17 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
+          <t>Produce foul sewage</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3004,12 +3008,12 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3023,24 +3027,20 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Connect to drainage system (oil and gas)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3050,32 +3050,28 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3085,11 +3081,19 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
+          <t>Hazardous substance consent required</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3097,62 +3101,58 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent details</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3191,28 +3191,24 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3231,23 +3227,23 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3266,27 +3262,23 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3302,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -3339,24 +3331,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3365,20 +3365,24 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Hours not known</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3388,19 +3392,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Additional information</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3408,44 +3404,60 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas ownership and notices</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3476,13 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3480,7 +3492,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3499,13 +3511,13 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3534,13 +3546,13 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3569,13 +3581,13 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3585,7 +3597,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3599,23 +3611,19 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice served date</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3629,29 +3637,29 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
+          <t>Parish or ward</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3660,15 +3668,19 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>Valid posted notices[]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Notice location</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3678,7 +3690,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3687,24 +3699,24 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice posted date</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3718,24 +3730,24 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Parish or ward</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3749,25 +3761,29 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Notice location</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3776,25 +3792,29 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Notice posted date</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3823,7 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -3811,7 +3831,7 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3830,55 +3850,55 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3892,7 +3912,7 @@
       <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -3900,12 +3920,12 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3919,7 +3939,7 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
@@ -3927,12 +3947,12 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3946,7 +3966,7 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -3954,12 +3974,12 @@
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -3969,11 +3989,19 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="2" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -3981,7 +4009,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4000,7 +4028,7 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
@@ -4008,7 +4036,7 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -4027,24 +4055,20 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New right of way</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4054,36 +4078,24 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
-        </is>
-      </c>
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -4097,7 +4109,7 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Temporary right of way changes</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -4105,12 +4117,12 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -4120,19 +4132,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -4140,12 +4144,12 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4159,15 +4163,19 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -4177,19 +4185,31 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="2" t="n"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Additional materials and specifications that form part of the planning application</t>
+        </is>
+      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
@@ -4204,7 +4224,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4233,7 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Inspection address</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
@@ -4221,26 +4241,34 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n"/>
-      <c r="B119" s="2" t="n"/>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
@@ -4248,51 +4276,39 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -4306,19 +4322,15 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4337,24 +4349,20 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -4368,24 +4376,20 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4395,8 +4399,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="2" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -4404,19 +4416,19 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -4435,19 +4447,19 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4466,19 +4478,19 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -4497,19 +4509,19 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4528,19 +4540,19 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -4550,41 +4562,33 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
-        </is>
-      </c>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4593,29 +4597,29 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4624,15 +4628,19 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4642,7 +4650,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4651,15 +4659,19 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -4669,37 +4681,41 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Site Visit Details</t>
+          <t>Site ownership</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4713,20 +4729,24 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4740,7 +4760,7 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
@@ -4748,7 +4768,7 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Details of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -4758,7 +4778,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4767,19 +4787,15 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Applicant interest adjoining land</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -4794,28 +4810,32 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n"/>
-      <c r="B137" s="2" t="n"/>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -4829,24 +4849,20 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -4856,19 +4872,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Storage facilities</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
-        </is>
-      </c>
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -4876,7 +4884,7 @@
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4886,37 +4894,33 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4930,15 +4934,19 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -4948,37 +4956,33 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -4988,11 +4992,19 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="2" t="n"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Storage facilities</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
+        </is>
+      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Storage facilities description</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5000,12 +5012,12 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -5017,18 +5029,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types</t>
+          <t>Trade effluent</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5036,12 +5047,12 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -5055,19 +5066,15 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -5077,33 +5084,37 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission type</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5117,24 +5128,20 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -5144,33 +5151,38 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Condition number</t>
-        </is>
-      </c>
+          <t>Oil and gas permission types[]</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5179,15 +5191,19 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5197,7 +5213,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5206,20 +5222,24 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission type</t>
+        </is>
+      </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -5233,25 +5253,29 @@
       <c r="B151" s="2" t="n"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5260,19 +5284,19 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
+          <t>Related permissions[]</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Condition number</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -5282,7 +5306,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5291,29 +5315,25 @@
       <c r="B153" s="2" t="n"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Application type</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5342,20 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Will consolidate permissions</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5349,19 +5365,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
-        </is>
-      </c>
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr"/>
@@ -5369,17 +5377,17 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5388,15 +5396,19 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5415,20 +5427,24 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Application type</t>
+        </is>
+      </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -5442,34 +5458,46 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Development phase</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
@@ -5477,12 +5505,12 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -5496,7 +5524,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5504,17 +5532,17 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5551,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5531,17 +5559,17 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5578,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5558,17 +5586,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5605,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5585,7 +5613,7 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -5595,24 +5623,16 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5620,17 +5640,17 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5659,7 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Agreement summary</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5647,15 +5667,131 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
+          <t>Who provided the site hectares value (applicant or system)</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Is an Environmental Statement attached to the application</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement reference</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Reference to the environmental statement document</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Draft agreement included</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Agreement summary</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
           <t>Summary of the agreement</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5663,66 +5799,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B91:B105"/>
-    <mergeCell ref="A83:A90"/>
-    <mergeCell ref="B139"/>
-    <mergeCell ref="A59:A64"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="B66:B75"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A76:A80"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A115:A119"/>
-    <mergeCell ref="A120:A128"/>
-    <mergeCell ref="A58"/>
-    <mergeCell ref="A144:A154"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="B54"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A106:A112"/>
-    <mergeCell ref="A133:A138"/>
-    <mergeCell ref="A155:A163"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="B115:B119"/>
-    <mergeCell ref="B58"/>
-    <mergeCell ref="A91:A105"/>
-    <mergeCell ref="A129:A132"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A54"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A66:A75"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B106:B112"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="B155:B163"/>
-    <mergeCell ref="B83:B90"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="A139"/>
-    <mergeCell ref="B144:B154"/>
-    <mergeCell ref="B129:B132"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B133:B138"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B120:B128"/>
-    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="B143"/>
+    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="A124:A132"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A67:A76"/>
+    <mergeCell ref="A137:A142"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="A143"/>
+    <mergeCell ref="A159:A167"/>
+    <mergeCell ref="B92:B109"/>
+    <mergeCell ref="A59"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B42:B47"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B124:B132"/>
+    <mergeCell ref="B59"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="B66"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B67:B76"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="A92:A109"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="B137:B142"/>
+    <mergeCell ref="A66"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="B84:B91"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A119:A123"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="A148:A158"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B159:B167"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="B144:B145"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
+++ b/generated/spreadsheet/development-relating-to-the-onshore-extraction-of-oil-and-gas-extraction-oil-gas.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,14 +1486,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1509,19 +1525,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,58 +1547,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1606,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1646,18 +1658,18 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1667,47 +1679,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1715,18 +1731,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1771,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1802,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1837,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1860,58 +1872,66 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk area</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Is the site within an area at risk of flooding?</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1920,20 +1940,32 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1943,11 +1975,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1955,17 +1995,17 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1974,7 +2014,7 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1982,17 +2022,17 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2041,7 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2009,17 +2049,17 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2068,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2036,12 +2076,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2051,19 +2091,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2071,7 +2103,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2090,7 +2122,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2098,26 +2130,34 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2125,34 +2165,26 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2160,17 +2192,17 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2211,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2187,26 +2219,34 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2214,7 +2254,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2233,7 +2273,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Archaeological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2241,7 +2281,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2256,19 +2296,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2276,12 +2308,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2291,19 +2323,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Archaeological features impact</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2311,12 +2335,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Where is there a likelihood of features of archaeological conservation importance being affected?</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2326,11 +2350,19 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2338,12 +2370,12 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2353,11 +2385,19 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2365,12 +2405,12 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2380,19 +2420,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Designated areas</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Designations[]</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2400,12 +2432,12 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>List of designated areas that apply to the site</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2415,36 +2447,24 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2454,28 +2474,32 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Designated areas</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Details of any 'designated area' the develpoment site is on, such as a Conservation Area or National Park.</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Designations[]</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>List of designated areas that apply to the site</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2485,8 +2509,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2494,19 +2526,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2520,19 +2552,19 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2551,24 +2583,24 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2587,19 +2619,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2609,32 +2641,28 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Equipment and method</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>How oil and gas will be extracted as part of the proposed development.</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Equipment plan</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Proposed employees</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2644,36 +2672,28 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2683,23 +2703,27 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Equipment and method</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>How oil and gas will be extracted as part of the proposed development.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Use details</t>
-        </is>
-      </c>
+          <t>Equipment plan</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Details of equipment to be used as part of the application including the maximum height and type of drilling rig to be used</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2709,13 +2733,21 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2723,19 +2755,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2749,25 +2781,29 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2776,15 +2812,19 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2794,7 +2834,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2843,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2811,17 +2851,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2870,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2838,17 +2878,17 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2897,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2865,17 +2905,17 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2924,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2892,7 +2932,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2911,7 +2951,7 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2919,34 +2959,26 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2954,7 +2986,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -2973,7 +3005,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -2981,12 +3013,12 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -2996,11 +3028,19 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>How waste water will leave the property as part of the proposed development</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Produce foul sewage</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3008,7 +3048,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposed development will produce any foul sewage</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3027,7 +3067,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system (oil and gas)</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3035,7 +3075,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3045,7 +3085,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3054,24 +3094,20 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Produce foul sewage</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposed development will produce any foul sewage</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3081,19 +3117,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent required</t>
+          <t>Connect to drainage system (oil and gas)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3101,12 +3129,12 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
+          <t>Whether the proposal needs to connect to the existing drainage system (oil and gas applications)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3120,15 +3148,19 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance consent details</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substance consent requirements</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3138,41 +3170,37 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation</t>
+          <t>Hazardous substances</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent required</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the use or storage of any substances requiring hazardous substances consent</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3186,19 +3214,15 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Use other</t>
-        </is>
-      </c>
+          <t>Hazardous substance consent details</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Details of hazardous substance consent requirements</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -3213,8 +3237,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3222,18 +3254,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -3257,23 +3285,19 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3297,22 +3321,18 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3336,27 +3356,23 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3370,24 +3386,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3396,15 +3420,27 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Additional information</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3414,45 +3450,33 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas ownership and notices</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3466,23 +3490,15 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Any additional information (such as hours of use of other machinery within the site-generators, pumps, etc)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3492,13 +3508,21 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas ownership and notices</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Ownership, agricultural tenant and public notice details for extraction of oil and gas applications</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Owners and tenants[]</t>
@@ -3511,13 +3535,13 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3527,7 +3551,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3546,13 +3570,13 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3581,13 +3605,13 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -3597,7 +3621,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3635,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3637,19 +3669,27 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Parish or ward</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Parish or ward where the notice was posted</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3659,7 +3699,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3668,19 +3708,27 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Notice location</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Location where the notice was posted</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3690,7 +3738,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3699,19 +3747,19 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Valid posted notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Notice posted date</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was posted</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3721,7 +3769,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3778,7 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3761,7 +3809,7 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3792,7 +3840,7 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Invalid posted notices[]</t>
+          <t>Valid posted notices[]</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3823,15 +3871,19 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>Invalid posted notices[]</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Parish or ward</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
+          <t>Parish or ward where the notice was posted</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3841,7 +3893,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3850,19 +3902,19 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice location</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Location where the notice was posted</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -3881,19 +3933,19 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Invalid posted notices[]</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Notice posted date</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Date when the notice was posted</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3912,7 +3964,7 @@
       <c r="B107" s="2" t="n"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -3920,7 +3972,7 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Steps taken to protect or replace notices that were removed, obscured or defaced</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -3930,7 +3982,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3939,20 +3991,24 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3966,15 +4022,19 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -3989,19 +4049,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -4009,12 +4061,12 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -4028,7 +4080,7 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
@@ -4036,12 +4088,12 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4055,7 +4107,7 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -4063,12 +4115,12 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -4078,11 +4130,19 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="2" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
@@ -4090,7 +4150,7 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4109,7 +4169,7 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Temporary right of way changes</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -4117,7 +4177,7 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Are temporary changes to rights of way needed while the site is worked</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4136,7 +4196,7 @@
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Future new right of way</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -4144,7 +4204,7 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided after extraction?</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -4163,24 +4223,20 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4190,36 +4246,24 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Plans, drawings and supporting materials</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Additional materials and specifications that form part of the planning application</t>
-        </is>
-      </c>
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Temporary right of way changes</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Are temporary changes to rights of way needed while the site is worked</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -4233,7 +4277,7 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Inspection address</t>
+          <t>Future new right of way</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
@@ -4241,12 +4285,12 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Full postal address where supporting material can be inspected</t>
+          <t>Will new public rights of way be provided after extraction?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -4256,32 +4300,28 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -4291,19 +4331,31 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="n"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Plans, drawings and supporting materials</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Additional materials and specifications that form part of the planning application</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -4313,7 +4365,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4374,7 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Inspection address</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -4330,7 +4382,7 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Full postal address where supporting material can be inspected</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -4340,16 +4392,24 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n"/>
-      <c r="B122" s="2" t="n"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -4357,17 +4417,17 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4436,7 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4384,7 +4444,7 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -4399,36 +4459,24 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -4442,24 +4490,20 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -4473,19 +4517,15 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -4500,8 +4540,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="2" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -4509,24 +4557,24 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4540,24 +4588,28 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4571,19 +4623,23 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -4602,19 +4658,23 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -4633,14 +4693,18 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4664,19 +4728,19 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -4686,41 +4750,33 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Site ownership</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
-        </is>
-      </c>
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4729,29 +4785,29 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Site owner</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4760,42 +4816,58 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Details of the applicant's interest in the land</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n"/>
-      <c r="B136" s="2" t="n"/>
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Site ownership</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>For oil and gas extraction developments, who owns or has an interest in the site.</t>
+        </is>
+      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest adjoining land</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the adjacent land</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -4810,32 +4882,28 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
+          <t>Site owner</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -4849,7 +4917,7 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
@@ -4857,12 +4925,12 @@
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Details of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -4876,7 +4944,7 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Applicant interest adjoining land</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -4884,7 +4952,7 @@
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Description of the applicant's interest in the adjacent land</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4894,33 +4962,37 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4934,24 +5006,20 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -4965,19 +5033,15 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -4987,32 +5051,28 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Storage facilities</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>For oil and gas extraction developments, how chemicals will be stored</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Storage facilities description</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -5027,32 +5087,28 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
-        </is>
-      </c>
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -5066,15 +5122,19 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -5084,24 +5144,24 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Trees and hedges information</t>
+          <t>Storage facilities</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>For oil and gas extraction developments, how chemicals will be stored</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Storage facilities description</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5109,12 +5169,12 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Details and proposed facilities for the storage of oil, fuel and chemicals and the proposed means of their protection</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5124,11 +5184,19 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5136,7 +5204,7 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5151,20 +5219,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission types</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
-</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Oil and gas permission types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -5172,43 +5231,47 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>List of permission types being applied for</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="2" t="n"/>
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application that permission was received for</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -5222,24 +5285,20 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Oil and gas permission type</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>An oil and gas related permission type</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -5249,28 +5308,33 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission types</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module for details about types of onshore oil and gas extraction permissions already received and applying for
+</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Related permissions[]</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Oil and gas permission types[]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>List of permission types being applied for</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5289,14 +5353,14 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Condition number</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Number of any condition being breached</t>
+          <t>The reference for the related application that permission was received for</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -5306,7 +5370,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5315,25 +5379,29 @@
       <c r="B153" s="2" t="n"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Other details</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Oil and gas permission type</t>
+        </is>
+      </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Explanation if other ground is selected</t>
+          <t>An oil and gas related permission type</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5342,20 +5410,24 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Will consolidate permissions</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant looking to consolidate permissions?</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5369,15 +5441,19 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
+          <t>Related permissions[]</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Condition number</t>
+        </is>
+      </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Details about the consolidation or update of permissions</t>
+          <t>Number of any condition being breached</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -5396,19 +5472,15 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Other details</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Explanation if other ground is selected</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5418,7 +5490,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5427,24 +5499,20 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Application type</t>
-        </is>
-      </c>
+          <t>Will consolidate permissions</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>The type of planning application</t>
+          <t>Is the applicant looking to consolidate permissions?</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -5458,59 +5526,51 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Related proposals[]</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Details about the consolidation or update of permissions</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Development type</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Development phase</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Phases of oil and gas development the application covers</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -5524,20 +5584,24 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Development description</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Application type</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Brief description of the development, including main oils, gases, and machinery</t>
+          <t>The type of planning application</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -5551,20 +5615,24 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Quantity cubic metres</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Related proposals[]</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Decision date</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Quantity of oil or gas involved in cubic metres</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5574,11 +5642,19 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Development type</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting information for developments used for oil and gas exploration or mining </t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Permission period years</t>
+          <t>Development phase</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5586,17 +5662,17 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Period of permission sought in years</t>
+          <t>Phases of oil and gas development the application covers</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5681,7 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block</t>
+          <t>Development description</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5613,7 +5689,7 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Hydrocarbon licence block where the development is located</t>
+          <t>Brief description of the development, including main oils, gases, and machinery</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -5632,7 +5708,7 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Surface site area hectares</t>
+          <t>Quantity cubic metres</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5640,7 +5716,7 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Surface site area in hectares</t>
+          <t>Quantity of oil or gas involved in cubic metres</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -5650,7 +5726,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5735,7 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Site hectares provided by</t>
+          <t>Permission period years</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr"/>
@@ -5667,12 +5743,12 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site hectares value (applicant or system)</t>
+          <t>Period of permission sought in years</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -5686,7 +5762,7 @@
       <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement</t>
+          <t>Hydrocarbon licence block</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr"/>
@@ -5694,12 +5770,12 @@
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Is an Environmental Statement attached to the application</t>
+          <t>Hydrocarbon licence block where the development is located</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -5713,7 +5789,7 @@
       <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Environmental statement reference</t>
+          <t>Surface site area hectares</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr"/>
@@ -5721,12 +5797,12 @@
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Reference to the environmental statement document</t>
+          <t>Surface site area in hectares</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -5736,19 +5812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Voluntary agreement</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
-        </is>
-      </c>
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Draft agreement included</t>
+          <t>Site hectares provided by</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr"/>
@@ -5756,17 +5824,17 @@
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Has an outline or draft agreement been included? (True / False)</t>
+          <t>Who provided the site hectares value (applicant or system)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5843,7 @@
       <c r="B169" s="2" t="n"/>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Agreement summary</t>
+          <t>Environmental statement</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr"/>
@@ -5783,15 +5851,104 @@
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
+          <t>Is an Environmental Statement attached to the application</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Environmental statement reference</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Reference to the environmental statement document</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary agreement</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Details of any voluntary agreements made as part of an oil and gas extraction application.</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Draft agreement included</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Has an outline or draft agreement been included? (True / False)</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Agreement summary</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
           <t>Summary of the agreement</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -5799,66 +5956,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="B143"/>
-    <mergeCell ref="B148:B158"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A124:A132"/>
+    <mergeCell ref="A162:A170"/>
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B68"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B94:B112"/>
+    <mergeCell ref="A113:A119"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A137:A142"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="A143"/>
-    <mergeCell ref="A159:A167"/>
-    <mergeCell ref="B92:B109"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B124:B132"/>
-    <mergeCell ref="B59"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="B66"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="B110:B116"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B67:B76"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="A92:A109"/>
-    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="A68"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A151:A161"/>
+    <mergeCell ref="B140:B145"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="B136:B139"/>
+    <mergeCell ref="B162:B170"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B151:B161"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B127:B135"/>
+    <mergeCell ref="B86:B93"/>
+    <mergeCell ref="A94:A112"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A61"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A136:A139"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="B113:B119"/>
+    <mergeCell ref="A146"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="A127:A135"/>
+    <mergeCell ref="A86:A93"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="B137:B142"/>
-    <mergeCell ref="A66"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A119:A123"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="A148:A158"/>
-    <mergeCell ref="A55"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B69:B78"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61"/>
+    <mergeCell ref="B57"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A140:A145"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B159:B167"/>
-    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A57"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="B146"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
